--- a/src/attributions/attributions_ig_traj_192.xlsx
+++ b/src/attributions/attributions_ig_traj_192.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1325596479805452</v>
+        <v>-0.05528238289280349</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -1011,52 +1011,52 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0295461924198502</v>
+        <v>-0.01521181842486179</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2776285541184297</v>
+        <v>0.112074202303832</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.106917653986966</v>
+        <v>-0.06001059350187293</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.009630752303574108</v>
+        <v>-0.003888046729681267</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2223636775622847</v>
+        <v>0.1157312355650137</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03198519879561309</v>
+        <v>-0.04610913374746394</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,10 +1065,10 @@
         <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05689973500830451</v>
+        <v>0.004228016233227912</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1089186502865644</v>
+        <v>0.06799047630454019</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.08260661680849585</v>
+        <v>-0.002111465490630281</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01655490321469943</v>
+        <v>0.1195397717502912</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.03935560699952714</v>
+        <v>0.06657116438663011</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1107,22 +1107,22 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.06526673827723177</v>
+        <v>-0.03276526204323058</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.08377200744450095</v>
+        <v>-0.07435295302359572</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1508125144811636</v>
+        <v>0.1013733697024754</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.2003786317984795</v>
+        <v>-0.1283984162140813</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1146,13 +1146,13 @@
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1300536553700075</v>
+        <v>-0.05323511892213322</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.4661272795929176</v>
+        <v>0.2835059635978781</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1019315961424422</v>
+        <v>0.07705490282139497</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
@@ -1173,25 +1173,25 @@
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.02417121635232534</v>
+        <v>0.07968579969431606</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.05425659100188865</v>
+        <v>-0.01168686672981791</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.1058893177997798</v>
+        <v>0.01663079786915575</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
@@ -1200,25 +1200,25 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.04980552648711953</v>
+        <v>-0.04883639228396024</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.004398305146162258</v>
+        <v>0.01315348560577752</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1631417456000037</v>
+        <v>-0.149977244673812</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
@@ -1227,13 +1227,13 @@
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.09199871832778382</v>
+        <v>-0.04963515701734013</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.2568295767399469</v>
+        <v>0.2018707174459535</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,52 +1245,52 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.09292330088689864</v>
+        <v>0.07148336394611221</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.003324894880627208</v>
+        <v>0.01397142766142745</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.08622221159529987</v>
+        <v>-0.08670453270060868</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0009946480603000942</v>
+        <v>0.003039709618568255</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.002911495236058416</v>
+        <v>0.001052151578220428</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.002498518338736247</v>
+        <v>-0.005983778517432203</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>0</v>
@@ -1299,46 +1299,46 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.06537516985287585</v>
+        <v>0.07479098754595322</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.007360786804887426</v>
+        <v>0.00278818783755981</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.09983264599801532</v>
+        <v>-0.08099060615449463</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.05863451258385064</v>
+        <v>0.0222673062039199</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.1735872646522105</v>
+        <v>0.01745511364371649</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.04102589065778278</v>
+        <v>-0.01954129585596495</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
@@ -1347,40 +1347,40 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01607925980330027</v>
+        <v>-0.01480689322176639</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.04530295771333684</v>
+        <v>-0.05449523518159803</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.008143588201298469</v>
+        <v>-0.09188886864338421</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.09043174607147236</v>
+        <v>0.008769855325891675</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,64 +1389,64 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.008775654299256266</v>
+        <v>-0.01447252048966296</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.09177307012437178</v>
+        <v>-0.06430340897778937</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.05549943907466821</v>
+        <v>0.03383458642181108</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.06665323662234698</v>
+        <v>0.006864875959906693</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.06154536705711426</v>
+        <v>0.0002503530137971242</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.026609708148491</v>
+        <v>0.06911882859613051</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.02475985850273873</v>
+        <v>0.01178180267772406</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0.004331758356435968</v>
+        <v>0.007532391325599587</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
@@ -1455,55 +1455,55 @@
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.06482023757872163</v>
+        <v>0.07812532010713785</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.01343543298078949</v>
+        <v>0.02595909542453748</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.09497476679395349</v>
+        <v>-0.0840712136502792</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.04386343206213528</v>
+        <v>0.0772973614848642</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02706278697379791</v>
+        <v>-0.009319552082147351</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.08479250515587512</v>
+        <v>0.04995400538837681</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>-0</v>
@@ -1515,7 +1515,7 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.05216584623000506</v>
+        <v>0.1252232026880308</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
@@ -1524,37 +1524,37 @@
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01756090338889561</v>
+        <v>0.02918654876941212</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.07192841997914616</v>
+        <v>0.06209370949062023</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.00213555786426776</v>
+        <v>0.06824611457707747</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.08267886847429701</v>
+        <v>-0.02034338140109571</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06683828911842679</v>
+        <v>0.1687862015222384</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.02273766107103135</v>
+        <v>-0.02483144452375674</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02425491315148753</v>
+        <v>-0.09118729117724571</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,13 +1592,13 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05121846351366165</v>
+        <v>0.2059326296414792</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,64 +1607,64 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.02101595613811584</v>
+        <v>-0.07965246039150856</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.02276778103160125</v>
+        <v>-0.09102367469826754</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01633431150023209</v>
+        <v>0.0906032314011575</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01055208517117251</v>
+        <v>-0.08411706499351884</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01254536051030162</v>
+        <v>-0.021470316846743</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004121784644244086</v>
+        <v>-0.002701315661671769</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.009124635463044787</v>
+        <v>-0.1798669863326122</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.003665884380847915</v>
+        <v>0.009624761342570315</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1673,40 +1673,40 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.008092224686457605</v>
+        <v>0.07032471319908359</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.01918069407562068</v>
+        <v>-0.01135033640896774</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0129942416549228</v>
+        <v>-0.02987327465182414</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0971539332918098</v>
+        <v>0.3777475559675858</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.008808726209790011</v>
+        <v>-0.2154916377064754</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.01836468545159951</v>
+        <v>-0.1227230609708017</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.02637494937591453</v>
+        <v>-0.01378249597728389</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,16 +1742,16 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0615331784058313</v>
+        <v>-0.02005243170381951</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.04881952876082857</v>
+        <v>-0.09117730556502296</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03505589985416163</v>
+        <v>0.04963994899173043</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,37 +1769,37 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02054332387517647</v>
+        <v>0.08870358436176043</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02155182616029998</v>
+        <v>0.0454975082688724</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.04180182571539127</v>
+        <v>0.2260220128116578</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.01552320983918893</v>
+        <v>-0.06041932784548697</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.002857280452661095</v>
+        <v>-0.1328535612566051</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1808,187 +1808,187 @@
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.02185431416917163</v>
+        <v>-0.09818954355945478</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0007882613757868945</v>
+        <v>0.02437833153381812</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.01739835042109649</v>
+        <v>0.09091177247992854</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0005574651877753846</v>
+        <v>-0.01544805639570631</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0003680763633037602</v>
+        <v>0.004895661737043317</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.0007470704001217782</v>
+        <v>-0.003201895504655938</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.01531424525833571</v>
+        <v>-0.09819966610837874</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.003706337431959918</v>
+        <v>0.02104981586622067</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01872135504987369</v>
+        <v>0.1069237015676148</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.01376528015335258</v>
+        <v>-0.03948800977892965</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02368097293992542</v>
+        <v>-0.0453430784457429</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.001044540808603807</v>
+        <v>0.03167957590708106</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.004005123600715156</v>
+        <v>-0.02459904734968323</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01784323491443598</v>
+        <v>-0.05385923890359594</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.007394951304354211</v>
+        <v>-0.01380851206993531</v>
       </c>
       <c r="DT3" t="n">
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.03386893442787201</v>
+        <v>-0.06889617642321973</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01791466953574379</v>
+        <v>0.0245461319786223</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01358498748725337</v>
+        <v>0.07831460968708211</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0204647742873071</v>
+        <v>-0.02345475312887155</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.003098217425834757</v>
+        <v>-0.002927122415376774</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.01448990289364832</v>
+        <v>0.03490127061564949</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.009812493303619439</v>
+        <v>-0.01610328396784396</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.006794212969962391</v>
+        <v>-0.03737300119690488</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.001479928696325481</v>
+        <v>0.07540896203812122</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.01546926730086737</v>
+        <v>-0.114784887764586</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,16 +2039,16 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.005903259287382938</v>
+        <v>0.005188947530464382</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.02302554659989057</v>
+        <v>0.0842392826127405</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>-0</v>
@@ -2057,25 +2057,25 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.02049137052293495</v>
+        <v>0.1233139586439599</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.01662596139332302</v>
+        <v>-0.0833181953088164</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.01165572835126054</v>
+        <v>0.07523287181865397</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.003515255631533317</v>
+        <v>0.03623691624551852</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,37 +2093,37 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.01991128506145687</v>
+        <v>-0.06333117122800153</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.005038631712644738</v>
+        <v>-0.01073768528026246</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002474377831257899</v>
+        <v>-0.02413355664964482</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.01554495380139698</v>
+        <v>0.08974863378365489</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,43 +2140,43 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2648990402019546</v>
+        <v>0.2353733376436543</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06364140287672218</v>
+        <v>-0.07839306342329959</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07191386436743992</v>
+        <v>-0.05410155477906965</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1882078033791055</v>
+        <v>0.2608273046357167</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05873128424689916</v>
+        <v>-0.1059848238929392</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.05330417648261011</v>
+        <v>-0.1164737847705808</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2194,70 +2194,70 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09416760408445721</v>
+        <v>0.05720382977004805</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.03030098059636517</v>
+        <v>-0.03741424251598174</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07758638818348287</v>
+        <v>-0.08940073064772508</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04987567131224008</v>
+        <v>-0.009850201850078582</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.002097180299950283</v>
+        <v>-0.1542226209465578</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.01740236260162581</v>
+        <v>-0.03310049458222812</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02270983974400179</v>
+        <v>0.08712679014222223</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.04960505299730634</v>
+        <v>-0.08084813143826346</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.04994810900760096</v>
+        <v>0.06524094769591551</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,34 +2266,34 @@
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3905040067708478</v>
+        <v>0.306664441190324</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.03200977409363412</v>
+        <v>-0.06810446301145984</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0493912438032896</v>
+        <v>-0.281191273191148</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,25 +2302,25 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.03988463035960109</v>
+        <v>0.005146985323950722</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.1215189061153849</v>
+        <v>-0.04476469417758509</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1269709545573439</v>
+        <v>0.02412687044939064</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,16 +2329,16 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.09065388094274644</v>
+        <v>0.01106427292644956</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.07141483016566899</v>
+        <v>0.04202506853227025</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.125689751849911</v>
+        <v>0.08003671207005704</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
@@ -2350,103 +2350,103 @@
         <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1840998620786753</v>
+        <v>0.1785631405404526</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.007373315317651106</v>
+        <v>-0.09953485935749436</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.03533067888082586</v>
+        <v>-0.104567444291339</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.09411233440386485</v>
+        <v>-0.1285523780849968</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.009635503310069224</v>
+        <v>0.1013578965095372</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001782539740064834</v>
+        <v>0.03547011606662907</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.001409433437527285</v>
+        <v>-0.01387260307236169</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.004627204655871276</v>
+        <v>0.008985469591184719</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.01135369257396618</v>
+        <v>0.007211084745504209</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06396327989885699</v>
+        <v>-0.1301223562474862</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02656051621945607</v>
+        <v>0.1162462718324239</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.006136689187345907</v>
+        <v>0.04338081676072716</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
@@ -2458,22 +2458,22 @@
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02181945762226763</v>
+        <v>-0.07622799695936343</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.05355042462501344</v>
+        <v>3.919477699518364e-05</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01858087002203559</v>
+        <v>-0.03954791720084396</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
@@ -2485,25 +2485,25 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07663346248126031</v>
+        <v>-0.06080687601075513</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.0112058557372158</v>
+        <v>-0.04532146169758358</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.04961405090530052</v>
+        <v>-0.06195085424856996</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2518,16 +2518,16 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.0381966733278794</v>
+        <v>-0.01717343853746612</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.03334485551282911</v>
+        <v>0.05802297107308238</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01026238319736849</v>
+        <v>0.01744525374124641</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
@@ -2536,58 +2536,58 @@
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.07990268657284076</v>
+        <v>-0.0763522474910381</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001161588539049069</v>
+        <v>0.06788308337701915</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0748266662404817</v>
+        <v>0.04547308995557858</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0169718920761699</v>
+        <v>-0.05342877962211792</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.01041668589203739</v>
+        <v>0.04467815189276288</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.03681348732720119</v>
+        <v>0.02239270911970695</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,16 +2599,16 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06400992899520146</v>
+        <v>-0.1383653601905873</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0006485136987018916</v>
+        <v>0.1354009370328877</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01428090165400867</v>
+        <v>0.019277715881436</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
@@ -2617,25 +2617,25 @@
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.02880828116802735</v>
+        <v>0.1408027850236236</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.009921336993986994</v>
+        <v>0.1013492326910454</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.006691200379684304</v>
+        <v>-0.01139569152545456</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
@@ -2644,31 +2644,31 @@
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.04084474282386334</v>
+        <v>0.04232392245484752</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.02779985044900109</v>
+        <v>0.1902671003464372</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.06537713071189176</v>
+        <v>-0.04474993646762199</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.05256130193450508</v>
+        <v>-0.0465041459334345</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.05220353247274824</v>
+        <v>0.04148127618042176</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,15 +2701,15 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1410202782558627</v>
+        <v>0.2015087882827337</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02579296822356879</v>
+        <v>0.008832671389168937</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07882343671008296</v>
+        <v>-0.1571838707134219</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1149352144948177</v>
+        <v>0.2557232805764192</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,64 +2745,64 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00560216294862142</v>
+        <v>-0.07619773662051622</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06349529566387704</v>
+        <v>-0.167138383790765</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02486221085034998</v>
+        <v>0.09524881074351432</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.03882555453073414</v>
+        <v>-0.05359710639944983</v>
       </c>
       <c r="X5" t="n">
-        <v>0.007953206099217533</v>
+        <v>-0.06703665597682279</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.00366154530372284</v>
+        <v>-0.03479815546073088</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01030698646265549</v>
+        <v>-0.1635822108018739</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.01104328905903841</v>
+        <v>0.06093839468582308</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -2817,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0285425844770852</v>
+        <v>0.1136816662555732</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005938713057855526</v>
+        <v>-0.003892202149601039</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.04392575069612908</v>
+        <v>-0.07351692288668184</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2844,34 +2844,34 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1481300511189013</v>
+        <v>0.4866222743713132</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.05168577225969324</v>
+        <v>-0.204528775342306</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.08266090042861632</v>
+        <v>-0.1761005830301949</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.06111238188573443</v>
+        <v>-0.09960983888230406</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,52 +2880,52 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0278838993387512</v>
+        <v>-0.007527455116034876</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.05938349331437833</v>
+        <v>-0.0562948849992443</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.05561734711797324</v>
+        <v>0.08703974442836956</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02511140931994077</v>
+        <v>0.01816003836746756</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01270509173770959</v>
+        <v>0.05698631590581078</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.08232317751242886</v>
+        <v>0.2897646828099211</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,91 +2934,91 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.03309360632430882</v>
+        <v>-0.06714537670102694</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.03097297870566606</v>
+        <v>-0.1671925799586078</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.03833787590266918</v>
+        <v>-0.1265656175447178</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.004987176429769227</v>
+        <v>0.02860946101413292</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.03977461585273488</v>
+        <v>0.08505544410677045</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001049258113982049</v>
+        <v>-0.04694086833253814</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001416367136546059</v>
+        <v>0.03293719970098148</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.001635803509596689</v>
+        <v>-0.001066267819364123</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03423707695073189</v>
+        <v>-0.1182827976514623</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.002506715589714907</v>
+        <v>0.01667061625584979</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.04461884527778701</v>
+        <v>0.1054798521902325</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3027,13 +3027,13 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.05052523770300458</v>
+        <v>-0.101308693983745</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
@@ -3042,25 +3042,25 @@
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0548247292459323</v>
+        <v>-0.03277410078996038</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0008467604903610016</v>
+        <v>0.0286565067489722</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01960381105687268</v>
+        <v>-0.1062684540659365</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,67 +3069,67 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02044551779355115</v>
+        <v>0.02997968440331831</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.005302105553416011</v>
+        <v>0.1573936511732467</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.04419225231264957</v>
+        <v>-0.05833062817400143</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01743247987512856</v>
+        <v>0.0918020030027885</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.02563456933576336</v>
+        <v>0.01708952510682664</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03038991310809848</v>
+        <v>-0.04081412368330629</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.007778460140320567</v>
+        <v>-0.03964954511134561</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.04018846782319158</v>
+        <v>0.02599058868087734</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02687275141575664</v>
+        <v>-0.0318284881283607</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01632540345980725</v>
+        <v>-0.1087098938771099</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.005577923106071601</v>
+        <v>0.0267020106284029</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,34 +3168,34 @@
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0346001036596696</v>
+        <v>-0.1340047200148723</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.0002240284847396851</v>
+        <v>0.001492719765589038</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.04413143916719909</v>
+        <v>0.101721222699002</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02344656844886248</v>
+        <v>0.07580462755230376</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,64 +3204,64 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.009773127294445251</v>
+        <v>-0.0147669447743872</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.03340830886636971</v>
+        <v>0.1068929183547704</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.006505755616033635</v>
+        <v>0.05707066229066221</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.0325039344304392</v>
+        <v>-0.05570597652873685</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02686016396421205</v>
+        <v>-0.02088249057128386</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0007681062586894554</v>
+        <v>-0.01771087548876747</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.01861151155108751</v>
+        <v>0.1148247918943325</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3270,7 +3270,7 @@
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.105393607392874</v>
+        <v>0.2832275625025632</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03862591179466556</v>
+        <v>-0.04008643136300927</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06662024249647405</v>
+        <v>-0.1882951302530481</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09218639070948313</v>
+        <v>0.3762457073836938</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,64 +3314,64 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02775152064041153</v>
+        <v>-0.1569937078462069</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.04207145342588373</v>
+        <v>-0.1496243211913337</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01197178530850308</v>
+        <v>0.1246878288380968</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01364792404645785</v>
+        <v>-0.127595063672073</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01455155825535077</v>
+        <v>-0.01436556341489707</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002242225910422958</v>
+        <v>-0.01746676404911722</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.007627847054635488</v>
+        <v>-0.2485127230839589</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.006208549645664025</v>
+        <v>0.03032806732741581</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.008324544445089087</v>
+        <v>0.06610935668407214</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01568531989472562</v>
+        <v>-0.03835706685208139</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01436509116944706</v>
+        <v>-0.02136791280577623</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1091754340393463</v>
+        <v>0.5179461084391882</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,25 +3422,25 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.03669851705789688</v>
+        <v>-0.2942258899239366</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.05013403933667113</v>
+        <v>-0.2054961001066058</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03930204194752713</v>
+        <v>-0.05036479468796659</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.06080138089730613</v>
+        <v>-0.01670522631010368</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.05735288126050353</v>
+        <v>-0.110889799295056</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03933351222411553</v>
+        <v>0.0687648575546926</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02841351658683119</v>
+        <v>0.1045698354027385</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01779833351607879</v>
+        <v>0.05569350922896975</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.05414113951792002</v>
+        <v>0.3029787903547357</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01566437857453054</v>
+        <v>-0.09145820274915895</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.01197632225145324</v>
+        <v>-0.106989416912537</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,148 +3515,148 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.02764364976824194</v>
+        <v>-0.1310496851615393</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002673894631209749</v>
+        <v>0.03525727402622833</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.02650585125103443</v>
+        <v>0.1008776312480682</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001044078235766537</v>
+        <v>-0.05493823451706907</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004414831211043778</v>
+        <v>0.04289412113420577</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.007518047943929835</v>
+        <v>0.03854001740774602</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.02039472769586598</v>
+        <v>-0.1349765829567921</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.00731297993397732</v>
+        <v>0.02604317935420485</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02868066624101028</v>
+        <v>0.1285848658824544</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.03447946934573446</v>
+        <v>-0.08096932689126471</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0383600096285184</v>
+        <v>-0.1501347986699728</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0003480882909733979</v>
+        <v>0.03543732105898681</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.007928235444414461</v>
+        <v>-0.02885060514350518</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.005385347577786728</v>
+        <v>-0.07084754530504034</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.005879935292152946</v>
+        <v>0.02061797151759243</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02996500409784866</v>
+        <v>-0.02909016546044193</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01884052139693086</v>
+        <v>-0.0001595147486211558</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02155046834119102</v>
+        <v>0.09687467420603023</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,28 +3677,28 @@
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02724540126222329</v>
+        <v>-0.05771603922375268</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01344778616172645</v>
+        <v>0.006744304070362359</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.03024571752233485</v>
+        <v>0.03253540753317712</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,37 +3707,37 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.01368021858918679</v>
+        <v>-0.01497512065526038</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01945940696908119</v>
+        <v>-0.01190513941654449</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.001534280044703618</v>
+        <v>0.1114175422456035</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01968967036175339</v>
+        <v>-0.1499151378222721</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,43 +3746,43 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.01032058013238543</v>
+        <v>0.004503766294184686</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03140297005211409</v>
+        <v>0.09191037303808236</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01679051861931863</v>
+        <v>0.2101564110355418</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0159748079566695</v>
+        <v>-0.06998426469410322</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01496293674793574</v>
+        <v>0.1285195439350169</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,46 +3791,46 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004508800564165339</v>
+        <v>0.050931121643411</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0239823349732586</v>
+        <v>-0.07810080430218319</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001727154148208447</v>
+        <v>-0.09536503972263018</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.005322960670697717</v>
+        <v>-0.03342678394748459</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.005368888271155104</v>
+        <v>0.1300105647484201</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,7 +3839,7 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3041267767614614</v>
+        <v>0.3231924340002356</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07944696767260467</v>
+        <v>-0.1574474856984551</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0337671603386641</v>
+        <v>-0.0463482763137618</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2281530196259798</v>
+        <v>0.3511406980690668</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0654441519635853</v>
+        <v>-0.14449582555669</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04450167181251637</v>
+        <v>-0.1053017331868169</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09520426892144021</v>
+        <v>0.04924007132295743</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0169547063983432</v>
+        <v>-0.03309842746641012</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05978503822968013</v>
+        <v>-0.1128579684055137</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,43 +3928,43 @@
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1319022583999126</v>
+        <v>-0.02802150053440534</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.04610901995692983</v>
+        <v>-0.1469341927268848</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.06551759911350233</v>
+        <v>-0.08955256619830691</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02616553386563628</v>
+        <v>0.1257859440853083</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.06803660098714695</v>
+        <v>-0.121333864045971</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0476210516078717</v>
+        <v>0.01602135288536183</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,16 +3982,16 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3555154206267067</v>
+        <v>0.3512102689747046</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.02396879432876483</v>
+        <v>-0.2537966742790898</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1246799456520706</v>
+        <v>-0.3447488891394216</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03255030966877175</v>
+        <v>-0.03703015587206291</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.05551148549638381</v>
+        <v>-0.02079783036646823</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1760332552659136</v>
+        <v>0.06121724172154895</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,76 +4036,76 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03579652113615843</v>
+        <v>0.02971412516063013</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.09546420936147998</v>
+        <v>0.1048685104532388</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1088155932183493</v>
+        <v>0.01312217992016203</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.202392100328228</v>
+        <v>0.2573501456768331</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0009175871886238721</v>
+        <v>-0.1699032474227</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.04900493908349321</v>
+        <v>-0.1198990013304092</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.08999001611180633</v>
+        <v>-0.1430010109757761</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01727573185775867</v>
+        <v>0.1846524949780959</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.002528439247817448</v>
+        <v>0.01014995527147892</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,49 +4117,49 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01359587497526173</v>
+        <v>-0.02935831351470632</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.02271059506019469</v>
+        <v>0.05965536492576685</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02025952320216804</v>
+        <v>0.02796366470161803</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.07541447755884395</v>
+        <v>-0.1350638285101804</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04047462635582431</v>
+        <v>0.1911969260975924</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.002143794457877505</v>
+        <v>0.02583406340817293</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,22 +4171,22 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01171508161622276</v>
+        <v>-0.09217969328015178</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0005064193716877428</v>
+        <v>-0.01454797744859072</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0005158961975796625</v>
+        <v>-0.1281813144431907</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4195,25 +4195,25 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.05732808368393926</v>
+        <v>-0.07257639520211834</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.0537891126798741</v>
+        <v>0.07069617948379317</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.07017128268831267</v>
+        <v>-0.008947323173724224</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4222,106 +4222,106 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01253964608854623</v>
+        <v>0.005942283753524317</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.02166087378417396</v>
+        <v>0.08226374559247093</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01426526995046999</v>
+        <v>-0.02167735170364419</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.05557419230016485</v>
+        <v>-0.08687490173899323</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02889320963818383</v>
+        <v>0.1306301411940085</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.09170814535274439</v>
+        <v>0.03465822094495143</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.07823818281081436</v>
+        <v>-0.06898503872046434</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.08543434209851064</v>
+        <v>-0.1164081652566985</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01285914379528745</v>
+        <v>-0.03542310064310383</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.07920099059611359</v>
+        <v>-0.1551642205343335</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02680567836240331</v>
+        <v>0.2138370339984647</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.006436687019389604</v>
+        <v>-0.003491838856021417</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4333,49 +4333,49 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.00744759997392381</v>
+        <v>0.1481265500203002</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.04965294011384581</v>
+        <v>0.1652531964776545</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.03095888140158225</v>
+        <v>0.008241731363338204</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.002443531002751255</v>
+        <v>0.04994094956009525</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.07387986065508181</v>
+        <v>0.2355011723908654</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02707628372713808</v>
+        <v>-0.05190050385717333</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,39 +4384,39 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02408872291696919</v>
+        <v>-0.05504192022865539</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.02974876786586001</v>
+        <v>0.1437758895577512</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1774618845533465</v>
+        <v>0.3267278418791099</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04804408566546823</v>
+        <v>0.02406191874875207</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1175756295394787</v>
+        <v>-0.2994092411231976</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,13 +4437,13 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1521067439743989</v>
+        <v>0.4095087179897669</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01627300610532379</v>
+        <v>-0.1249078739959048</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.07696903691843332</v>
+        <v>-0.2866756528864594</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03182302377754161</v>
+        <v>0.1200614154582821</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
@@ -4479,37 +4479,37 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02862698168781971</v>
+        <v>-0.07804943586715693</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0003495146993050758</v>
+        <v>-0.09125517577351512</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.00228482560609198</v>
+        <v>-0.07070651874472823</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0008747245431520338</v>
+        <v>-0.2317141333113936</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.008968006854129093</v>
+        <v>0.07110474651469686</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -4518,28 +4518,28 @@
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02640756563704421</v>
+        <v>0.1311233889063309</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.009683204145728116</v>
+        <v>-0.03667330238049162</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05310058128740785</v>
+        <v>-0.08925492589453622</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1528534643943812</v>
+        <v>0.6005830446290951</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.03734727186145556</v>
+        <v>-0.2840621283746746</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1161542728417131</v>
+        <v>-0.3341586469428531</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.05233599532775377</v>
+        <v>-0.1302135184988792</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,25 +4587,25 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04833762042083375</v>
+        <v>0.02537528550495153</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.0491269410728273</v>
+        <v>-0.04948546557955492</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04964417299871704</v>
+        <v>0.122603175158843</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,79 +4614,79 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02317401838687887</v>
+        <v>0.06006134488654192</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.004534260766278887</v>
+        <v>0.07595451907731803</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.08830141853826382</v>
+        <v>0.3282128859413526</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02551131689542412</v>
+        <v>-0.08303979108529336</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03422336445025529</v>
+        <v>-0.1900692109545795</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.0426960855627903</v>
+        <v>-0.1604278534875037</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002064841516864209</v>
+        <v>0.04702512115010715</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03709441325662847</v>
+        <v>0.1081047025755514</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002524096796776107</v>
+        <v>-0.08753840176149605</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
@@ -4695,37 +4695,37 @@
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001137313638678613</v>
+        <v>0.09963615112846497</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.01292647560800126</v>
+        <v>-0.007977278208731564</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03780652974364755</v>
+        <v>-0.1515039884947151</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.006945445538257791</v>
+        <v>0.02850391881786214</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04040790321084167</v>
+        <v>0.1413611711041263</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4734,25 +4734,25 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.00611381714759533</v>
+        <v>0.02385372150422842</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05425811866621269</v>
+        <v>-0.02759887334081863</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001849885853411415</v>
+        <v>0.03909356381199871</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02003496397438697</v>
+        <v>-0.135302937176847</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,25 +4776,25 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01486257327730923</v>
+        <v>0.02808381033978298</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.009253161033919382</v>
+        <v>0.1787556096428484</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.04823800017351424</v>
+        <v>-0.1007681039403984</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
@@ -4803,37 +4803,37 @@
         <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.03128580391230212</v>
+        <v>0.1072658518521084</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.01650633670439284</v>
+        <v>0.05381994443565959</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03632211996327393</v>
+        <v>-0.0283609205348149</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
         <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01284293478245575</v>
+        <v>-0.03643655403467658</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03734275217215383</v>
+        <v>0.01052564012963434</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,13 +4842,13 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03403833236071764</v>
+        <v>-0.04228860564171729</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
@@ -4857,13 +4857,13 @@
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.005873485944490737</v>
+        <v>-0.1131297656285994</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.006608376008677746</v>
+        <v>0.02491066170184096</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03780404859297667</v>
+        <v>-0.1747840917684477</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
@@ -4884,25 +4884,25 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.008499741856094388</v>
+        <v>0.02042971761116</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03833762558058384</v>
+        <v>0.1297150203163657</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02331342039897978</v>
+        <v>0.09936886280870076</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.01144635592023375</v>
+        <v>-0.03999822995791748</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03574985519741991</v>
+        <v>0.1478808204125222</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.002933223403480311</v>
+        <v>0.02798053055444245</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,37 +4938,37 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02663353189099168</v>
+        <v>-0.07360766302314259</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.021875456413417</v>
+        <v>-0.02349412265553791</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.003310714661828454</v>
+        <v>-0.03917366038157794</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01871974115312633</v>
+        <v>0.1530369439561523</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,7 +4977,7 @@
         <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,46 +4985,46 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2966100372177339</v>
+        <v>0.2650235815935421</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09251972744736088</v>
+        <v>-0.1379324905865146</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06748450314023292</v>
+        <v>0.0004349970177664199</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03727931121430023</v>
+        <v>-0.0986521905440574</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2462414960894206</v>
+        <v>0.3572314264604474</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06323117368119831</v>
+        <v>-0.1642965293081073</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04989109041129199</v>
+        <v>-0.07528796732193727</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.03758790430219033</v>
+        <v>-0.086287594564301</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,133 +5039,133 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.07824064031665799</v>
+        <v>0.1069363088159009</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02495468807201317</v>
+        <v>-0.091270943377357</v>
       </c>
       <c r="W9" t="n">
-        <v>0.041574818616316</v>
+        <v>-0.1216784981544768</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01134099364354196</v>
+        <v>-0.0868788456875534</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05498497229725322</v>
+        <v>-0.1005251922778254</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01204503911599231</v>
+        <v>-0.116016493005078</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01354466039631152</v>
+        <v>-0.09928937726451728</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.01708847235848042</v>
+        <v>0.07013341621967789</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01905949238737632</v>
+        <v>0.08355906004428459</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05663539425623951</v>
+        <v>-0.0813820618535807</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05403336755295805</v>
+        <v>0.0026366175817969</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.04219881775711441</v>
+        <v>-0.03875106505860565</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2885058195484158</v>
+        <v>0.4124387240801216</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.03749721060397475</v>
+        <v>-0.1546768629638886</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03235513206781332</v>
+        <v>-0.2218920322796608</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.02482680063354763</v>
+        <v>-0.1552104450500904</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.04818761496071487</v>
+        <v>-0.07897686238581599</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06299947960859739</v>
+        <v>-0.08627166866974063</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1092746393109315</v>
+        <v>0.009196117891978885</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.04926506270783808</v>
+        <v>-0.07655322976420117</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0675591551168373</v>
+        <v>0.03832113188737277</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.05108264766477009</v>
+        <v>0.1192452836990254</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.09918260135572098</v>
+        <v>-0.007089782682484685</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.03697479759525464</v>
+        <v>-0.004149789110640175</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5195,31 +5195,31 @@
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1345310958844833</v>
+        <v>0.247458160477787</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.00201939559197415</v>
+        <v>-0.1208391319740486</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02245707613755304</v>
+        <v>-0.06269209755008548</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01372309285657461</v>
+        <v>-0.1295617732772306</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.07142502792888485</v>
+        <v>-0.09389816087809043</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0104552731082974</v>
+        <v>0.1040599153501385</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.002659918355594485</v>
+        <v>0.0101282232832265</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02396518348049048</v>
+        <v>0.03189014068335585</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,46 +5255,46 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.003063618586850321</v>
+        <v>-0.03398708635356668</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.02718205369307522</v>
+        <v>0.1081822439394901</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.03244922505246275</v>
+        <v>0.06326796765863295</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.01659622414320707</v>
+        <v>0.02477747688141905</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.05861319959364533</v>
+        <v>-0.1021297703907073</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03199759872846165</v>
+        <v>0.1311437856435474</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001307611386036127</v>
+        <v>0.007471989605565393</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02543322536536964</v>
+        <v>0.05734106451857649</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03189863012438825</v>
+        <v>-0.04468476347183269</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.04326940263664507</v>
+        <v>0.03112955003656362</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.004164121119110139</v>
+        <v>0.008658707252920115</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01123783123593995</v>
+        <v>0.02136016027009907</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5330,31 +5330,31 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.01978872254523345</v>
+        <v>-0.009863185598840484</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03752325915282668</v>
+        <v>0.03268664825647465</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01744772156067373</v>
+        <v>-0.07932596235267823</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0192804475848472</v>
+        <v>-0.01216308865538179</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,76 +5363,76 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03701863200230176</v>
+        <v>-0.02073822932834549</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01582650519299933</v>
+        <v>0.08015446326707294</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.02080704078435784</v>
+        <v>0.009718159876766589</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.03469767167618117</v>
+        <v>-0.02407523121696089</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0762907810176289</v>
+        <v>-0.04982838985179795</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03275148298971785</v>
+        <v>0.09146056534737228</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05245926360818354</v>
+        <v>0.02292942428992237</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.01751778003416754</v>
+        <v>-0.04528716709403947</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.05635133774628693</v>
+        <v>-0.04053373728621922</v>
       </c>
       <c r="EQ9" t="n">
         <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02473642064280961</v>
+        <v>0.1015589165809334</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01348342162660755</v>
+        <v>-0.01373765349412954</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.03290528997694995</v>
+        <v>0.0565151092256442</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,22 +5444,22 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05899816198360345</v>
+        <v>-0.1040000081025627</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01352119096938438</v>
+        <v>0.147197193774934</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.004753226497370896</v>
+        <v>-0.006511477387165269</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.03145827143646546</v>
+        <v>0.04406568618917246</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5468,52 +5468,52 @@
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.03097377320343571</v>
+        <v>0.1184556621397233</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0362130091591101</v>
+        <v>0.118410885851253</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.009190056019668423</v>
+        <v>-0.02287918713009233</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.01099178370024969</v>
+        <v>0.1281788053253084</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.004925342165696881</v>
+        <v>0.01477864957724929</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.009754397028229767</v>
+        <v>0.1449261815928986</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0319724870451904</v>
+        <v>-0.04733007337410144</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01902404609222003</v>
+        <v>-0.02024695528159818</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,25 +5522,25 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01709206540651812</v>
+        <v>-0.01811262352142722</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.05282979881343404</v>
+        <v>0.03145786624234143</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.03038564527008909</v>
+        <v>0.1089046105800843</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>0</v>
@@ -5554,46 +5554,46 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2375549490567123</v>
+        <v>0.1636963602384493</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07163675892320907</v>
+        <v>-0.09442201750671539</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01925165910869601</v>
+        <v>-0.005563540478323244</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1863934418944772</v>
+        <v>0.1998069219682524</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07482456409222045</v>
+        <v>-0.1186311800472918</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02972661046220002</v>
+        <v>-0.03678810146079305</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,19 +5608,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06743187703244223</v>
+        <v>0.06150579585842699</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01319258291935494</v>
+        <v>-0.04578432097692119</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0738339722057602</v>
+        <v>-0.04195412530171205</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
@@ -5629,76 +5629,76 @@
         <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.05845901465798675</v>
+        <v>-0.006074818309184563</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01969840305982016</v>
+        <v>-0.09647457126188039</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01722052389682318</v>
+        <v>-0.03271300127037642</v>
       </c>
       <c r="AG10" t="n">
         <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01731976884951594</v>
+        <v>0.07355966968191101</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.05694668517625593</v>
+        <v>-0.06764489395293863</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.04653137091004816</v>
+        <v>0.03093935468959871</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2243260286965259</v>
+        <v>0.1922824697208796</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.02318118332061579</v>
+        <v>-0.07540790618295933</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1025279677833229</v>
+        <v>-0.1365999449639604</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,34 +5707,34 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02993841906775955</v>
+        <v>-0.01648984838296468</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.09923443314862934</v>
+        <v>-0.03323647788628697</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06293298310761275</v>
+        <v>-0.0346796034212501</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,19 +5743,19 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0496643369697654</v>
+        <v>0.02979396299776483</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.03138441799034126</v>
+        <v>0.01999691625570401</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1490614150393862</v>
+        <v>0.03995858495553389</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5764,49 +5764,49 @@
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.09679724515103988</v>
+        <v>0.1280317194141427</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03040308348578757</v>
+        <v>-0.05718090296955282</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.07347792370648491</v>
+        <v>-0.04155342954210864</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05949784281672935</v>
+        <v>-0.05542161080564443</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.0003030521941976983</v>
+        <v>0.07067525687560641</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.008272652267834048</v>
+        <v>0.0003494111815714656</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.00647385925864961</v>
+        <v>-0.02950128393918903</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.03811525444324815</v>
+        <v>0.1138980423472525</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05392370130594729</v>
+        <v>0.0336941335984301</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5851,43 +5851,43 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.046162031981967</v>
+        <v>-0.0502004542002408</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0143452144869735</v>
+        <v>0.08075068124603889</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.004858823721089496</v>
+        <v>0.004153827098783501</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.03118906382127288</v>
+        <v>-0.03261457983441085</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01792964553151672</v>
+        <v>0.03911591388630645</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01313078210774799</v>
+        <v>-0.05078429665130634</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5902,28 +5902,28 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.02786180268549819</v>
+        <v>-0.04263882199318132</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.05635164862323917</v>
+        <v>-0.04513951027016454</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01748202857764404</v>
+        <v>-0.02312542686541474</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,73 +5932,73 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03959586839725406</v>
+        <v>-0.009416342043884984</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.002363252370538335</v>
+        <v>0.04948252811761838</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01487609660832076</v>
+        <v>-0.05796491823241793</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.06099423501286922</v>
+        <v>-0.02657892064409464</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02404440214188631</v>
+        <v>0.0520195722839988</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04984714770632032</v>
+        <v>0.02960457015029163</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.04442506737572906</v>
+        <v>0.02120651450941127</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01197678256792502</v>
+        <v>0.02009309025968634</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.03209548342385718</v>
+        <v>-0.02518831535020219</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6007,49 +6007,49 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0471441917167273</v>
+        <v>-0.06049851991208113</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.004511494091944238</v>
+        <v>0.09360168073125158</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.007837215839428587</v>
+        <v>-0.01456453096897911</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03391642873225893</v>
+        <v>0.08495852283241145</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.009748860922205853</v>
+        <v>0.06588784209648087</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.04003038956592191</v>
+        <v>-0.02927234062714132</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6058,28 +6058,28 @@
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.001325058454232322</v>
+        <v>0.0006446867539111021</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.003346667008543039</v>
+        <v>0.08639554229241743</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.005775166050470295</v>
+        <v>-0.01727612202708984</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6091,39 +6091,39 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.02257652514041972</v>
+        <v>-0.01366722903743068</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.085187614260617</v>
+        <v>0.0258604532569747</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3270061975876245</v>
+        <v>0.4015879358322397</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08896715240750655</v>
+        <v>-0.0001882057447845785</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2158640818302616</v>
+        <v>-0.3422955556509796</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,13 +6144,13 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3103632988364848</v>
+        <v>0.5606472512156052</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02850021387719847</v>
+        <v>-0.07919614953543239</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2229273735923359</v>
+        <v>-0.4770548975740098</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03962797669571628</v>
+        <v>0.1627048036281291</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.02706734574189182</v>
+        <v>-0.100516856780441</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01149821315342154</v>
+        <v>-0.07681069439391298</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.007460433677973328</v>
+        <v>-0.02146908679322361</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03104874100264686</v>
+        <v>-0.3231835310994855</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.007016606274025094</v>
+        <v>0.09822810317314436</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6225,28 +6225,28 @@
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04973740039457255</v>
+        <v>0.1274165660415132</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.003414382254529652</v>
+        <v>-0.07569000952853519</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.07427894615197138</v>
+        <v>-0.08570097939008484</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2473136761282198</v>
+        <v>0.7103432133705951</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.02703313644466197</v>
+        <v>-0.3200330369759922</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.0856595152129732</v>
+        <v>-0.2050850564224694</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07255580731143055</v>
+        <v>-0.1265820638866519</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,25 +6294,25 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.06576769046280416</v>
+        <v>-0.02412870640013874</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.08846981214792121</v>
+        <v>-0.03749282787907415</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.06227753872661084</v>
+        <v>0.1405754899757987</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,37 +6321,37 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01810381293350538</v>
+        <v>0.07798654766294806</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01864966166978327</v>
+        <v>0.03822615613975494</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1326663733927211</v>
+        <v>0.4029047270374253</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.04414900240911659</v>
+        <v>-0.04756815935078262</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.04832743820775708</v>
+        <v>-0.1879791455927431</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,28 +6360,28 @@
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.06799653321921585</v>
+        <v>-0.1542639096692359</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.007754356771684821</v>
+        <v>0.04003815383036168</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.04472624179740071</v>
+        <v>0.1102257639806059</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,49 +6393,49 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.003106679741743236</v>
+        <v>-0.1799327466143662</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.02338628604142299</v>
+        <v>0.1430137008025651</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.07379886511405619</v>
+        <v>0.03970268200960417</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.06107179913725279</v>
+        <v>-0.1460944324662869</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.007787277786378805</v>
+        <v>0.02305537221882287</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04711530222866236</v>
+        <v>0.1440317130117701</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,19 +6447,19 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.05243375882188207</v>
+        <v>-0.1066935756049994</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06343444896983677</v>
+        <v>-0.07301248536587231</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.05127708252545429</v>
+        <v>0.08213527375141255</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02053390920616312</v>
+        <v>-0.07390425868674068</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02847861098977629</v>
+        <v>-0.006509586504683862</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01410245095436079</v>
+        <v>0.099499100330007</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,76 +6501,76 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.06072310049753631</v>
+        <v>-0.06332214758088676</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01827710642040244</v>
+        <v>-0.009372170108718391</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.03025763699963034</v>
+        <v>0.03926002827857847</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.0748881364524792</v>
+        <v>-0.03824657084447471</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.03065247630772401</v>
+        <v>-0.01099905053334348</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.03353200560139591</v>
+        <v>0.01942293605795607</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.04691657753268808</v>
+        <v>-0.05411049538857834</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.04136522695662299</v>
+        <v>-0.08519216887380864</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.007335051385062643</v>
+        <v>-0.01685535148772703</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6582,46 +6582,46 @@
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.06340822179503749</v>
+        <v>-0.1762360281984073</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.003152470826970344</v>
+        <v>-0.002137168163514947</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.04824617278321801</v>
+        <v>0.1230235973154088</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.0293547223353519</v>
+        <v>0.1360300182402241</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.005373695126452929</v>
+        <v>-0.08594624880855678</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.04135195473229911</v>
+        <v>0.1898006867657189</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.001427673693359327</v>
+        <v>0.01414632595351415</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.002836561464883065</v>
+        <v>-0.01081117184991514</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04859032408504889</v>
+        <v>-0.07873731441605294</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.009923257485090618</v>
+        <v>-0.0321722374902771</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.05077214274318714</v>
+        <v>0.1728423619044678</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5792437066328294</v>
+        <v>0.3563346611196312</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1274810186006819</v>
+        <v>-0.03092164831917627</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5091105243607013</v>
+        <v>-0.1426984252606821</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5760069712492182</v>
+        <v>0.5036583725829984</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05813319017185963</v>
+        <v>-0.1219332840142775</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5537183048372705</v>
+        <v>-0.2176796523836552</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04755236829990615</v>
+        <v>0.1064887658080962</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,37 +6755,37 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.110654745010335</v>
+        <v>-0.1166618233662825</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.02565384337818499</v>
+        <v>-0.005090410387975141</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.0275390229202471</v>
+        <v>-0.02931597959110936</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.0215953269672738</v>
+        <v>-0.2716371709374638</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.04212379964103503</v>
+        <v>-0.004549947446162852</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.09769455732862328</v>
+        <v>0.03627142449193518</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0006567358219328438</v>
+        <v>-0.03902280683020567</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.09125932246545443</v>
+        <v>0.0179704578611553</v>
       </c>
       <c r="AQ12" t="n">
         <v>-0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4681216858609668</v>
+        <v>0.4830067608289389</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.07547865179868263</v>
+        <v>-0.2471306261364534</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.2411337016768416</v>
+        <v>-0.1030859309087518</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1256404465667237</v>
+        <v>-0.02640743229741034</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1561352566964735</v>
+        <v>-0.01826023118805718</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.2061257706689008</v>
+        <v>-0.08055430902221697</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1601394364002145</v>
+        <v>0.05420754045649814</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.001140776253103799</v>
+        <v>0.07284421821868936</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01590004500465311</v>
+        <v>-0.03856732649621976</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2485805446403976</v>
+        <v>0.2599856884467435</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.07451044470466224</v>
+        <v>-0.07364203894135758</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.1461459617618215</v>
+        <v>-0.09421125771368159</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6929,28 +6929,28 @@
         <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09586491076524317</v>
+        <v>-0.1098733076809664</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.006446215008329582</v>
+        <v>0.02944543385110552</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.1165299558341483</v>
+        <v>0.04753346200453771</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,100 +6962,100 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.003115304557728661</v>
+        <v>-0.132883428025923</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01787048106919314</v>
+        <v>0.1103401426896391</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02395170569775671</v>
+        <v>0.1006350723349099</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07769714451202178</v>
+        <v>-0.1101429362917546</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.005546675415865648</v>
+        <v>0.008845732805488119</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.121821495728354</v>
+        <v>0.06877497437296268</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04474311101682561</v>
+        <v>-0.04971666937476797</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05347417951927155</v>
+        <v>-0.168019676363107</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.001451015452034701</v>
+        <v>0.04964933054648572</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.003472330483317901</v>
+        <v>-0.01092191807312633</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03362394520549131</v>
+        <v>-0.05045557676934236</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.007595696074924218</v>
+        <v>0.06265048639325359</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7064,13 +7064,13 @@
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.06633790709106792</v>
+        <v>-0.02029626083507293</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,25 +7079,25 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.02092571729254978</v>
+        <v>-0.07606006179769176</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0604119105792296</v>
+        <v>0.02755687738840463</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.108232070485527</v>
+        <v>-0.04202635601058043</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
@@ -7106,79 +7106,79 @@
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02331439806358535</v>
+        <v>0.02215210337803252</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1265440928468862</v>
+        <v>-0.009410661920081128</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03263884978846953</v>
+        <v>-0.01312609594229622</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.0146199236652245</v>
+        <v>-0.01706506412837016</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.07942412872194721</v>
+        <v>0.1215373664251312</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.07440339027998528</v>
+        <v>-0.1296503996940592</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.005603887711857129</v>
+        <v>0.000249308693892745</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1105132503528639</v>
+        <v>0.03831841965707554</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.003945683446421438</v>
+        <v>0.1922076591772191</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,16 +7187,16 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.0100714325585216</v>
+        <v>-0.09426401307233671</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.05596894958747622</v>
+        <v>0.109675009652774</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,46 +7205,46 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.005437178968010783</v>
+        <v>0.009855611703085876</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.009291071496026496</v>
+        <v>-0.0251904100577068</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03707465793457311</v>
+        <v>-0.05046906775903426</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.05130643391850202</v>
+        <v>-0.03420563764413689</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.05910585980061403</v>
+        <v>0.05732790399884384</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1544188935148341</v>
+        <v>0.3958643794029042</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07434624519471678</v>
+        <v>-0.02084509152020293</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07191094627322574</v>
+        <v>-0.1446385525758582</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1313128974087503</v>
+        <v>0.4986440986933964</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05300828472760943</v>
+        <v>-0.1279690718404325</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07991690897304321</v>
+        <v>-0.2041604031644494</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01285498906148165</v>
+        <v>0.08982252365081479</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,40 +8462,40 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.009143915894461702</v>
+        <v>-0.0746323075620289</v>
       </c>
       <c r="X15" t="n">
-        <v>0.008585893434490358</v>
+        <v>-0.009302112134788276</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.00708099261352923</v>
+        <v>-0.03024932641232912</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01095058767563661</v>
+        <v>-0.2307873373409146</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.008891241431807639</v>
+        <v>0.01709925190226669</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.009017842687066626</v>
+        <v>0.04035664814959713</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.008681091507523003</v>
+        <v>-0.02778306521480335</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01371395358608961</v>
+        <v>-0.0001885847210065052</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,25 +8531,25 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.09654125682359209</v>
+        <v>0.3938336471289925</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02558823624540049</v>
+        <v>-0.2563008768056509</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.01930057289415121</v>
+        <v>-0.1024042275531773</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.0302820312550028</v>
+        <v>0.00252955785861262</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.04866486776021819</v>
+        <v>-0.002904869744809502</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.0543366550675645</v>
+        <v>-0.04804601829997016</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03448809281252849</v>
+        <v>0.03959616992019722</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01721900225294691</v>
+        <v>0.04865757265505019</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01589760666920734</v>
+        <v>-0.02422771510152101</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.04605661846881794</v>
+        <v>0.2209306048771014</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.01045136467074858</v>
+        <v>-0.05304717578285637</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.01144505830400866</v>
+        <v>-0.09802608447146666</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8639,28 +8639,28 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02315840521840748</v>
+        <v>-0.1034167076342855</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.006584241803874971</v>
+        <v>0.02809609202439048</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01672923858127688</v>
+        <v>0.05187316016624946</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,76 +8669,76 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.001485202031397698</v>
+        <v>-0.1324474891003564</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.0073279866417078</v>
+        <v>0.1474936523834096</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01263667932660277</v>
+        <v>0.06768225135802683</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01765724039905513</v>
+        <v>-0.1010686269832201</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.005379815246833458</v>
+        <v>0.015331665117897</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01733536584598776</v>
+        <v>0.07164908613476234</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.0301532257095577</v>
+        <v>-0.08033913368697386</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.04821482242880116</v>
+        <v>-0.1956340256185488</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01088256427121481</v>
+        <v>0.06007360194547549</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,79 +8747,79 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.005855340341051488</v>
+        <v>-0.01837878589909518</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02068669027473315</v>
+        <v>-0.03498485093664613</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.007959741920477664</v>
+        <v>0.02766281593663096</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.02656132921347498</v>
+        <v>-0.006562249680281331</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01415902346671893</v>
+        <v>-0.06639004196760329</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.01832937144328398</v>
+        <v>0.0166167110461417</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.02815144169986555</v>
+        <v>-0.04669363257947479</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.006443556042594025</v>
+        <v>0.01152574949112689</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01244994054135613</v>
+        <v>0.004292513796186449</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8831,79 +8831,79 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.009990529301953644</v>
+        <v>-0.04251452547465764</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.002515272087712165</v>
+        <v>-0.0155457864232985</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.009720591527442599</v>
+        <v>0.0860015087308605</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.01816137902611428</v>
+        <v>-0.1214162651914464</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.008609350245061197</v>
+        <v>0.002555874606952007</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.0205748469995555</v>
+        <v>0.04479780620918175</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01363540422291733</v>
+        <v>0.1511574967464079</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01161635186728579</v>
+        <v>-0.08862515265782175</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01895218087121359</v>
+        <v>0.109636536573462</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,55 +8912,55 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>6.383140881813266e-05</v>
+        <v>0.00150547842735951</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.001260441709090497</v>
+        <v>-0.009248608646502012</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01957513267543856</v>
+        <v>-0.0243058301229967</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.003079416305427231</v>
+        <v>-0.02878331499979738</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.0048316269926084</v>
+        <v>0.0646616299022493</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
